--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:27:05+00:00</t>
+    <t>2023-06-08T09:38:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace}
 </t>
   </si>
   <si>

--- a/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitioner.xlsx
+++ b/ig/mc-changes-1.0.1/StructureDefinition-as-dp-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$195</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6320" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6353" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-08T09:38:17+00:00</t>
+    <t>2023-06-08T10:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2004,6 +2004,21 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>Type de diplôme, par exemple : DE, DES, CES, etc.</t>
+  </si>
+  <si>
+    <t>typeDiplome</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
@@ -2361,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ194"/>
+  <dimension ref="A1:AJ195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.60546875" customWidth="true" bestFit="true"/>
@@ -9497,7 +9512,7 @@
         <v>72</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10088,7 +10103,7 @@
         <v>90</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>117</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -21936,9 +21951,11 @@
         <v>643</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>71</v>
       </c>
@@ -21947,10 +21964,10 @@
         <v>72</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>71</v>
@@ -21959,19 +21976,19 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>274</v>
+        <v>645</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>276</v>
+        <v>646</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>71</v>
@@ -21996,13 +22013,11 @@
         <v>71</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>71</v>
+        <v>647</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>71</v>
@@ -22020,13 +22035,13 @@
         <v>71</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>90</v>
@@ -22037,10 +22052,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22051,7 +22066,7 @@
         <v>72</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>71</v>
@@ -22060,22 +22075,22 @@
         <v>71</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>293</v>
+        <v>92</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>645</v>
+        <v>274</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>646</v>
+        <v>275</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>647</v>
+        <v>277</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>71</v>
@@ -22124,7 +22139,7 @@
         <v>71</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>644</v>
+        <v>278</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>72</v>
@@ -22136,15 +22151,15 @@
         <v>90</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>298</v>
+        <v>117</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22167,18 +22182,20 @@
         <v>71</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>71</v>
       </c>
@@ -22226,7 +22243,7 @@
         <v>71</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>72</v>
@@ -22238,15 +22255,15 @@
         <v>90</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22260,7 +22277,7 @@
         <v>72</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>71</v>
@@ -22269,7 +22286,7 @@
         <v>71</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>653</v>
+        <v>300</v>
       </c>
       <c r="L194" t="s" s="2">
         <v>654</v>
@@ -22280,9 +22297,7 @@
       <c r="N194" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="O194" t="s" s="2">
-        <v>657</v>
-      </c>
+      <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>71</v>
       </c>
@@ -22306,11 +22321,13 @@
         <v>71</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="Y194" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="Z194" t="s" s="2">
-        <v>658</v>
+        <v>71</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>71</v>
@@ -22328,23 +22345,125 @@
         <v>71</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ194" t="s" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="195" hidden="true">
+      <c r="A195" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E195" s="2"/>
+      <c r="F195" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H195" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K195" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="M195" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="O195" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="P195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q195" s="2"/>
+      <c r="R195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X195" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="Y195" s="2"/>
+      <c r="Z195" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AA195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE195" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF195" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG195" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH195" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI195" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ195" t="s" s="2">
         <v>117</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ194">
+  <autoFilter ref="A1:AJ195">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22354,7 +22473,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI193">
+  <conditionalFormatting sqref="A2:AI194">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
